--- a/countries_en_fr_nl.xlsx
+++ b/countries_en_fr_nl.xlsx
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,4259 +414,5510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C250"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>nameEng</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>nameFr</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>nameNl</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Afghanistan</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Afghanistan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Afghanistan</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Albania</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Albanie</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Albanië</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>012</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Algérie</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Algerije</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>American Samoa</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Samoa américaines</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Amerikaans-Samoa</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>020</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Andorra</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Andorre</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Andorra</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Angola</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Angola</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Angola</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Anguilla</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Anguilla</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Anguilla</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Antarctica</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Antarctique</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Antarctica</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>028</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Antigua and Barbuda</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Antigua-et-Barbuda</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Antigua en Barbuda</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Argentine</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Argentinië</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>051</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Armenia</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Arménie</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Armenië</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Aruba</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Aruba</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Aruba</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Australie</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Australië</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Autriche</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Oostenrijk</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>031</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Azerbaijan</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Azerbaïdjan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Azerbeidzjan</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Bahamas</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Bahamas</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Bahama's</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Bahrain</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Bahreïn</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Bahrein</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>050</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>Bangladesh</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Bangladesh</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Bangladesh</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>052</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Barbados</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Barbade</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Barbados</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Belarus</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Bélarus</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Wit-Rusland</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Belgique</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>België</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>084</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Belize</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Belize</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Belize</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Benin</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Bénin</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Benin</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Bermuda</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Bermudes</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Bermuda</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Bhutan</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Bhoutan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Bhutan</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Bolivia</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Bolivie</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Bolivia</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Bonaire, Sint Eustatius and Saba</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Bonaire, Saint-Eustache et Saba</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Bonaire, Sint Eustatius en Saba</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>070</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Bosnie-Herzégovine</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Bosnië en Herzegovina</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>072</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Botswana</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Botswana</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Botswana</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>074</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Bouvet Island</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Île Bouvet</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Bouveteiland</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Brésil</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Brazilië</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>086</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>British Indian Ocean Territory</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Territoire britannique de l'océan Indien</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Brits Indische Oceaanterritorium</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>092</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>British Virgin Islands</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Îles Vierges britanniques</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Britse Maagdeneilanden</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>096</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>Brunei Darussalam</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Brunéi Darussalam</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Brunei</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Bulgarie</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Bulgarije</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Burkina Faso</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Burkina Faso</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Burkina Faso</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Burundi</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Burundi</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Burundi</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>Cabo Verde</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Cap-Vert</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Kaapverdië</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Cambodia</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Cambodge</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Cambodja</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Cameroun</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Kameroen</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Cayman Islands</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Îles Caïmans</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Kaaimaneilanden</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Central African Republic</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>République centrafricaine</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Centraal-Afrikaanse Republiek</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Chad</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Tchad</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Tsjaad</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Chili</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Chili</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Chine</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Christmas Island</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Île Christmas</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Christmaseiland</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Cocos (Keeling) Islands</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Îles Cocos (Keeling)</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Cocoseilanden (Keelingeilanden)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Colombie</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Comoros</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Comores</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Comoren</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Congo</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>République du Congo</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Congo</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Cook Islands</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Îles Cook</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Cookeilanden</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Costa Rica</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Croatie</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Kroatië</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Cuba</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Cuba</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Cuba</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Cyprus</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Chypre</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Czechia</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Tchéquie</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Tsjechië</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Ivoorkust</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Democratic Republic of the Congo</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>République démocratique du Congo</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Democratische Republiek Congo</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Danemark</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Denemarken</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>Djibouti</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Djibouti</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Djibouti</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Dominica</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Dominique</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Dominica</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Dominican Republic</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>République dominicaine</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Dominicaanse Republiek</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Équateur</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Égypte</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Egypte</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>El Salvador</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Salvador</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>El Salvador</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>Equatorial Guinea</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Guinée Équatoriale</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Equatoriaal-Guinea</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>Eritrea</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Érythrée</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Eritrea</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>Estonia</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Estonie</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Estland</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>Eswatini</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Eswatini</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Eswatini</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Éthiopie</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Ethiopië</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>Falkland Islands (Malvinas)</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Îles Malouines (Falkland)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Falklandeilanden (Malvinas)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>Faroe Islands</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Îles Féroé</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Faeröer</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>Fiji</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Fidji</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Fiji</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Finlande</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Frankrijk</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>French Guiana</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Guyane française</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Frans-Guyana</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
         <is>
           <t>French Polynesia</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Polynésie française</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Frans-Polynesië</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>French Southern Territories</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Terres australes françaises</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Franse Zuidelijke Gebieden</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>Gabon</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Gabon</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Gabon</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>Gambia</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Gambie</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Gambia</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>Georgia</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Géorgie</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Georgia</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Allemagne</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Duitsland</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>Gibraltar</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Gibraltar</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Gibraltar</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Grèce</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Griekenland</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>Greenland</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Groënland</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Groenland</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
         <is>
           <t>Grenada</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Grenade</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Grenada</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>Guadeloupe</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Guadeloupe</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Guadeloupe</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>Guam</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Guam</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Guam</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>Guernsey</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Guernesey</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Guernsey</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>Guinea</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Guinée</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Guinee</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>Guinea-Bissau</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Guinée-Bissau</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Guinee-Bissau</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
         <is>
           <t>Guyana</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Guyana</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Guyana</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Haïti</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Haïti</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>Heard Island and McDonald Islands</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Îles Heard-et-MacDonald</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Heardeiland en McDonaldeilanden</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
         <is>
           <t>Holy See (Vatican City State)</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Saint-Siège (état de la cité du Vatican)</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Vaticaanstad</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
         <is>
           <t>Honduras</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Honduras</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Honduras</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>Hongkong</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
         <is>
           <t>Hungary</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Hongrie</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>Hongarije</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
         <is>
           <t>Iceland</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Islande</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>IJsland</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Inde</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Indonésie</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Indonesië</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
         <is>
           <t>Iraq</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Irlande</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>Ierland</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
         <is>
           <t>Isle of Man</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Île de Man</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>Eiland Man</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
         <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Israël</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>Israël</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Italie</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>Italië</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
         <is>
           <t>Jamaica</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Jamaïque</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>Jamaica</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Japon</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
         <is>
           <t>Jersey</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Jersey</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>Jersey</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Jordanie</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>Jordanië</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
         <is>
           <t>Kazakhstan</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Kazakhstan</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>Kazachstan</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>Kenia</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
         <is>
           <t>Kiribati</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Kiribati</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>Kiribati</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
         <is>
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Koweït</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>Koeweit</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
         <is>
           <t>Kyrgyzstan</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Kirghizistan</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>Kirgizië</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
         <is>
           <t>Laos</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Laos</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>Laos</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
         <is>
           <t>Latvia</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Lettonie</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>Letland</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
         <is>
           <t>Lebanon</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Liban</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>Libanon</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
         <is>
           <t>Lesotho</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Lesotho</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>Lesotho</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
         <is>
           <t>Liberia</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Libéria</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>Liberia</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
         <is>
           <t>Libya</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Libye</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>Libië</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
         <is>
           <t>Liechtenstein</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Liechtenstein</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Liechtenstein</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Lituanie</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>Litouwen</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
         <is>
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>Luxemburg</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
         <is>
           <t>Macao</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>Macau</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
         <is>
           <t>Madagascar</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Madagascar</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>Madagaskar</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
         <is>
           <t>Malawi</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Malawi</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>Malawi</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Malaisie</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>Maleisië</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
         <is>
           <t>Maldives</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Maldives</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>Maldiven</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
         <is>
           <t>Mali</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Mali</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>Mali</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Malte</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
         <is>
           <t>Marshall Islands</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Îles Marshall</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>Marshalleilanden</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
         <is>
           <t>Martinique</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Martinique</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>Martinique</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
         <is>
           <t>Mauritania</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Mauritanie</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>Mauritanië</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
         <is>
           <t>Mauritius</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Maurice</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>Mauritius</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
         <is>
           <t>Mayotte</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Mayotte</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>Mayotte</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Mexique</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
         <is>
           <t>Micronesia</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Micronésie</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>Micronesië</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
         <is>
           <t>Moldova</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Moldavie</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>Moldavië</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
         <is>
           <t>Monaco</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Monaco</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>Monaco</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
         <is>
           <t>Mongolia</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Mongolie</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>Mongolië</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
         <is>
           <t>Montenegro</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Monténégro</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Montenegro</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
         <is>
           <t>Montserrat</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Montserrat</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>Montserrat</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
         <is>
           <t>Morocco</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Maroc</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
         <is>
           <t>Mozambique</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Mozambique</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Mozambique</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
         <is>
           <t>Myanmar</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Birmanie</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>Myanmar</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
         <is>
           <t>Namibia</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>Namibie</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>Namibië</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
         <is>
           <t>Nauru</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>Nauru</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>Nauru</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
         <is>
           <t>Nepal</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Népal</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>Nepal</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>Pays-Bas</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
         <is>
           <t>New Caledonia</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>Nouvelle-Calédonie</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>Nieuw-Caledonië</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Nouvelle-Zélande</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>Nieuw-Zeeland</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
         <is>
           <t>Nicaragua</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>Nicaragua</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Nicaragua</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
         <is>
           <t>Niger</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Niger</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Niger</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
         <is>
           <t>Niue</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>Nioue</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>Niue</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
         <is>
           <t>Norfolk Island</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>Île Norfolk</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>Norfolk</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
         <is>
           <t>North Korea</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Corée du Nord</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Noord-Korea</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
         <is>
           <t>North Macedonia</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>Macédoine du Nord</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>Noord-Macedonië</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
         <is>
           <t>Northern Mariana Islands</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>Îles Mariannes du Nord</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>Noordelijke Marianen</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>Norvège</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>Noorwegen</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
         <is>
           <t>Oman</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>Oman</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>Oman</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
         <is>
           <t>Palau</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>Palaos</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>Palau</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
         <is>
           <t>Palestine</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Palestine</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>Palestina</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
         <is>
           <t>Papua New Guinea</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>Papouasie-Nouvelle-Guinée</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>Papoea-Nieuw-Guinea</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
         <is>
           <t>Peru</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>Pérou</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>Peru</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Philippines</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>Filipijnen</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
         <is>
           <t>Pitcairn</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Îles Pitcairn</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Pitcairneilanden</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>Pologne</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>Polen</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
         <is>
           <t>Puerto Rico</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>Porto Rico</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Puerto Rico</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
         <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Roumanie</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>Roemenië</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
         <is>
           <t>Russia</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>Russie</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>Rusland</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
         <is>
           <t>Réunion</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>La Réunion</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>Réunion</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
         <is>
           <t>Saint Barthélemy</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Saint-Barthélemy</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>Saint-Barthélemy</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
         <is>
           <t>Saint Helena, Ascension and Tristan da Cunha</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>Sainte-Hélène, Ascension et Tristan da Cunha</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Sint-Helena, Ascension en Tristan da Cunha</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
         <is>
           <t>Saint Kitts and Nevis</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>Saint-Christophe-et-Niévès</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>Saint Kitts en Nevis</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
         <is>
           <t>Saint Lucia</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>Sainte-Lucie</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>Saint Lucia</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
         <is>
           <t>Saint Martin (French part)</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>Saint-Martin (partie française)</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>Sint-Maarten (Frans deel)</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
         <is>
           <t>Saint Pierre and Miquelon</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>Saint-Pierre-et-Miquelon</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>Saint-Pierre en Miquelon</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
         <is>
           <t>Saint Vincent and the Grenadines</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>Saint-Vincent-et-les-Grenadines</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>Saint Vincent en de Grenadines</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
         <is>
           <t>Samoa</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>Samoa</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>Samoa</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
         <is>
           <t>San Marino</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>Saint-Marin</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>San Marino</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
         <is>
           <t>Sao Tome and Principe</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>Sao Tomé-et-Principe</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="D195" t="inlineStr">
         <is>
           <t>Sao Tomé en Principe</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
         <is>
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>Arabie saoudite</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>Saoedi-Arabië</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>Sénégal</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
         <is>
           <t>Serbia</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>Serbie</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>Servië</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
         <is>
           <t>Seychelles</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>Seychelles</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>Seychellen</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
         <is>
           <t>Sierra Leone</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>Sierra Leone</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>Sierra Leone</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>Singapour</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
         <is>
           <t>Sint Maarten (Dutch part)</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>Saint-Martin (partie néerlandaise)</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>Sint Maarten (Nederlands deel)</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>Slovaquie</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>Slowakije</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>Slovénie</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>Slovenië</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>090</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
         <is>
           <t>Solomon Islands</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>Îles Salomon</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>Salomonseilanden</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
         <is>
           <t>Somalia</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>Somalie</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>Somalië</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
         <is>
           <t>South Africa</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>Afrique du Sud</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>Zuid-Afrika</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
         <is>
           <t>South Georgia and the South Sandwich Islands</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Géorgie du Sud et les îles Sandwich du Sud</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>Zuid-Georgia en de Zuidelijke Sandwicheilanden</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Corée du Sud</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>Zuid-Korea</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
         <is>
           <t>South Sudan</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>Soudan du Sud</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>Zuid-Soedan</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>Espagne</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>Spanje</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
         <is>
           <t>Sudan</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>Soudan</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>Soedan</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
         <is>
           <t>Suriname</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>Surinam</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>Suriname</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
         <is>
           <t>Svalbard and Jan Mayen</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="C215" t="inlineStr">
         <is>
           <t>Svalbard et île Jan Mayen</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>Spitsbergen en Jan Mayen</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>Suède</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>Zweden</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="C217" t="inlineStr">
         <is>
           <t>Suisse</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>Zwitserland</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
         <is>
           <t>Syria</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>Syrie</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>Syrië</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
         <is>
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>Taïwan</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>Taiwan</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
         <is>
           <t>Tajikistan</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>Tadjikistan</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>Tadzjikistan</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
         <is>
           <t>Tanzania</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>Tanzanie</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>Tanzania</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Thaïlande</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
         <is>
           <t>Timor-Leste</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>Timor oriental</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>Oost-Timor</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
         <is>
           <t>Tokelau</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>Tokelau</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>Tokelau</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
         <is>
           <t>Tonga</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>Tonga</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>Tonga</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
         <is>
           <t>Trinidad and Tobago</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>Trinité-et-Tobago</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>Trinidad en Tobago</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>Tunisie</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>Tunesië</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
         <is>
           <t>Turkmenistan</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>Turkménistan</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>Turkmenistan</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
         <is>
           <t>Turks and Caicos Islands</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>Îles Turques-et-Caïques</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>Turks- en Caicoseilanden</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
         <is>
           <t>Tuvalu</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="C231" t="inlineStr">
         <is>
           <t>Tuvalu</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>Tuvalu</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
         <is>
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="C232" t="inlineStr">
         <is>
           <t>Turquie</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>Turkije</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
         <is>
           <t>U.S. Virgin Islands</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="C233" t="inlineStr">
         <is>
           <t>Îles Vierges des États-Unis</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>Amerikaanse Maagdeneilanden</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>Ouganda</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>Oeganda</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
         <is>
           <t>Ukraine</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>Ukraine</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>Oekraïne</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
         <is>
           <t>United Arab Emirates</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="C236" t="inlineStr">
         <is>
           <t>Émirats arabes unis</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>Verenigde Arabische Emiraten</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="C237" t="inlineStr">
         <is>
           <t>Royaume-Uni</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>Verenigd Koninkrijk</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>États-Unis</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>Verenigde Staten</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
         <is>
           <t>United States Minor Outlying Islands</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>Îles mineures éloignées des États-Unis</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>Kleine afgelegen eilanden van de Verenigde Staten</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="C240" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
         <is>
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t>Ouzbékistan</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>Oezbekistan</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
         <is>
           <t>Vanuatu</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Vanuatu</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>Vanuatu</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>Viêt Nam</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
         <is>
           <t>Wallis and Futuna</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>Wallis et Futuna</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>Wallis en Futuna</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
         <is>
           <t>Western Sahara</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>Sahara occidental</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>Westelijke Sahara</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
         <is>
           <t>Yemen</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="C247" t="inlineStr">
         <is>
           <t>Yémen</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>Jemen</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
         <is>
           <t>Zambia</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>Zambie</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>Zambia</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
         <is>
           <t>Zimbabwe</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>Zimbabwe</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>Zimbabwe</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
         <is>
           <t>Åland Islands</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>Îles Åland</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>Ålandseilanden</t>
         </is>
